--- a/remisiones.xlsx
+++ b/remisiones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB5"/>
+  <dimension ref="A1:BB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1526,6 +1526,638 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>POL-25-00034</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>05/11/2025 13:05:44</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Camilo Vela</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1023013161</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ALLIANZ SEGUROS S.A.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>AU - AUTOMOVILES</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>123456</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Camilo Vela</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>1023013161</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Camilo Vela</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>1023013161</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1213800</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>120000</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Agencia Principal</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>120000</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>120000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>120000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>Contado</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Cobro mensual</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Prueba</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Prueba</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>Analista 1</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>Camilo_Vela_1023013161\POLIZAS\AU_-_AUTOMOVILES\2025-2026\AU_-_AUTOMOVILES_123456_ALLIANZ_SEGUROS_S.A._Recibo.pdf</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>POL-25-00035</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>06/11/2025 14:39:07</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Camilo</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>10230130161</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ALLIANZ SEGUROS S.A.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ARR - ARRENDAMIENTO</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>12345678</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Camilo</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>10230130161</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Camilo</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>10230130161</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>119000000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Agencia Principal</t>
+        </is>
+      </c>
+      <c r="AI7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>Contado</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cobro mensual</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Prueba</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Prueba</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>Analista 1</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>Camilo_10230130161\POLIZAS\ARR_-_ARRENDAMIENTO\2025-2026\ARR_-_ARRENDAMIENTO_12345678_ALLIANZ_SEGUROS_S.A._Recibo.pdf</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>POL-25-00036</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Gestionado</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>06/11/2025 14:42:20</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>10230130161</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ALLIANZ SEGUROS DE VIDA S.A.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>AP - ACCIDENTES PERSONALES</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>45345</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>10230130161</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>10230130161</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>11900014.28</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Agencia Principal</t>
+        </is>
+      </c>
+      <c r="AI8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>Contado</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cobro mensual</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Prueba</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>prueba</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>Analista 2</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>Pedro_10230130161.0\POLIZAS\AP_-_ACCIDENTES_PERSONALES\2025-2025\AP_-_ACCIDENTES_PERSONALES_45345_ALLIANZ_SEGUROS_DE_VIDA_S.A._Recibo.pdf</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>25-00004</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
